--- a/storage/data/syllabus.xlsx
+++ b/storage/data/syllabus.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
   <si>
     <t>DEPARTMENT</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>COURSE_CODE</t>
+  </si>
+  <si>
+    <t>IMPLEMENTATION_YEAR</t>
   </si>
   <si>
     <t>MODULE_TITLE</t>
@@ -352,8 +355,8 @@
     <col customWidth="1" min="1" max="1" width="19.75"/>
     <col customWidth="1" min="2" max="3" width="18.13"/>
     <col customWidth="1" min="4" max="4" width="13.88"/>
-    <col customWidth="1" min="5" max="5" width="27.38"/>
-    <col customWidth="1" min="6" max="6" width="13.88"/>
+    <col customWidth="1" min="5" max="6" width="27.38"/>
+    <col customWidth="1" min="7" max="7" width="13.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -375,145 +378,169 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2024.0</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025.0</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024.0</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2022.0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2024.0</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2024.0</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2021.0</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>26</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
